--- a/data_polls.xlsx
+++ b/data_polls.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W758"/>
+  <dimension ref="A1:W759"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -34421,6 +34421,58 @@
         <v>15</v>
       </c>
     </row>
+    <row r="759">
+      <c r="A759" s="2">
+        <v>45998</v>
+      </c>
+      <c r="B759" s="2">
+        <v>45995</v>
+      </c>
+      <c r="C759" s="2">
+        <v>45996</v>
+      </c>
+      <c r="D759" s="2">
+        <v>45995</v>
+      </c>
+      <c r="E759" t="inlineStr">
+        <is>
+          <t>Ireland Thinks</t>
+        </is>
+      </c>
+      <c r="F759">
+        <v>1069</v>
+      </c>
+      <c r="G759">
+        <v>20</v>
+      </c>
+      <c r="H759">
+        <v>17</v>
+      </c>
+      <c r="I759">
+        <v>24</v>
+      </c>
+      <c r="J759">
+        <v>5</v>
+      </c>
+      <c r="K759">
+        <v>2</v>
+      </c>
+      <c r="O759">
+        <v>3</v>
+      </c>
+      <c r="Q759">
+        <v>8</v>
+      </c>
+      <c r="R759">
+        <v>5</v>
+      </c>
+      <c r="S759">
+        <v>5</v>
+      </c>
+      <c r="W759">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data_polls.xlsx
+++ b/data_polls.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W759"/>
+  <dimension ref="A1:W760"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -34473,6 +34473,58 @@
         <v>11</v>
       </c>
     </row>
+    <row r="760">
+      <c r="A760" s="2">
+        <v>46047</v>
+      </c>
+      <c r="B760" s="2">
+        <v>46038</v>
+      </c>
+      <c r="C760" s="2">
+        <v>46043</v>
+      </c>
+      <c r="D760" s="2">
+        <v>46040</v>
+      </c>
+      <c r="E760" t="inlineStr">
+        <is>
+          <t>Red C</t>
+        </is>
+      </c>
+      <c r="F760">
+        <v>1010</v>
+      </c>
+      <c r="G760">
+        <v>15</v>
+      </c>
+      <c r="H760">
+        <v>18</v>
+      </c>
+      <c r="I760">
+        <v>24</v>
+      </c>
+      <c r="J760">
+        <v>5</v>
+      </c>
+      <c r="K760">
+        <v>2</v>
+      </c>
+      <c r="O760">
+        <v>3</v>
+      </c>
+      <c r="Q760">
+        <v>10</v>
+      </c>
+      <c r="R760">
+        <v>5</v>
+      </c>
+      <c r="S760">
+        <v>4</v>
+      </c>
+      <c r="W760">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data_polls.xlsx
+++ b/data_polls.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W760"/>
+  <dimension ref="A1:W761"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -34525,6 +34525,58 @@
         <v>14</v>
       </c>
     </row>
+    <row r="761">
+      <c r="A761" s="2">
+        <v>46054</v>
+      </c>
+      <c r="B761" s="2">
+        <v>46052</v>
+      </c>
+      <c r="C761" s="2">
+        <v>46052</v>
+      </c>
+      <c r="D761" s="2">
+        <v>46052</v>
+      </c>
+      <c r="E761" t="inlineStr">
+        <is>
+          <t>Ireland Thinks</t>
+        </is>
+      </c>
+      <c r="F761">
+        <v>1219</v>
+      </c>
+      <c r="G761">
+        <v>18</v>
+      </c>
+      <c r="H761">
+        <v>18</v>
+      </c>
+      <c r="I761">
+        <v>20</v>
+      </c>
+      <c r="J761">
+        <v>4</v>
+      </c>
+      <c r="K761">
+        <v>3</v>
+      </c>
+      <c r="O761">
+        <v>4</v>
+      </c>
+      <c r="Q761">
+        <v>10</v>
+      </c>
+      <c r="R761">
+        <v>6</v>
+      </c>
+      <c r="S761">
+        <v>6</v>
+      </c>
+      <c r="W761">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data_polls.xlsx
+++ b/data_polls.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W761"/>
+  <dimension ref="A1:W762"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -34577,6 +34577,58 @@
         <v>11</v>
       </c>
     </row>
+    <row r="762">
+      <c r="A762" s="2">
+        <v>46058</v>
+      </c>
+      <c r="B762" s="2">
+        <v>46052</v>
+      </c>
+      <c r="C762" s="2">
+        <v>46056</v>
+      </c>
+      <c r="D762" s="2">
+        <v>46054</v>
+      </c>
+      <c r="E762" t="inlineStr">
+        <is>
+          <t>Ipsos B&amp;A</t>
+        </is>
+      </c>
+      <c r="F762">
+        <v>1200</v>
+      </c>
+      <c r="G762">
+        <v>19</v>
+      </c>
+      <c r="H762">
+        <v>18</v>
+      </c>
+      <c r="I762">
+        <v>24</v>
+      </c>
+      <c r="J762">
+        <v>4</v>
+      </c>
+      <c r="K762">
+        <v>4</v>
+      </c>
+      <c r="O762">
+        <v>2</v>
+      </c>
+      <c r="Q762">
+        <v>7</v>
+      </c>
+      <c r="R762">
+        <v>3</v>
+      </c>
+      <c r="S762">
+        <v>4</v>
+      </c>
+      <c r="W762">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data_polls.xlsx
+++ b/data_polls.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W762"/>
+  <dimension ref="A1:W763"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -34629,6 +34629,58 @@
         <v>15</v>
       </c>
     </row>
+    <row r="763">
+      <c r="A763" s="2">
+        <v>46075</v>
+      </c>
+      <c r="B763" s="2">
+        <v>46066</v>
+      </c>
+      <c r="C763" s="2">
+        <v>46072</v>
+      </c>
+      <c r="D763" s="2">
+        <v>46069</v>
+      </c>
+      <c r="E763" t="inlineStr">
+        <is>
+          <t>Red C</t>
+        </is>
+      </c>
+      <c r="F763">
+        <v>1010</v>
+      </c>
+      <c r="G763">
+        <v>17</v>
+      </c>
+      <c r="H763">
+        <v>18</v>
+      </c>
+      <c r="I763">
+        <v>23</v>
+      </c>
+      <c r="J763">
+        <v>5</v>
+      </c>
+      <c r="K763">
+        <v>3</v>
+      </c>
+      <c r="O763">
+        <v>3</v>
+      </c>
+      <c r="Q763">
+        <v>9</v>
+      </c>
+      <c r="R763">
+        <v>5</v>
+      </c>
+      <c r="S763">
+        <v>4</v>
+      </c>
+      <c r="W763">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data_polls.xlsx
+++ b/data_polls.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W763"/>
+  <dimension ref="A1:W764"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -34681,6 +34681,58 @@
         <v>13</v>
       </c>
     </row>
+    <row r="764">
+      <c r="A764" s="2">
+        <v>46082</v>
+      </c>
+      <c r="B764" s="2">
+        <v>46080</v>
+      </c>
+      <c r="C764" s="2">
+        <v>46080</v>
+      </c>
+      <c r="D764" s="2">
+        <v>46080</v>
+      </c>
+      <c r="E764" t="inlineStr">
+        <is>
+          <t>Ireland Thinks</t>
+        </is>
+      </c>
+      <c r="F764">
+        <v>1308</v>
+      </c>
+      <c r="G764">
+        <v>18</v>
+      </c>
+      <c r="H764">
+        <v>17</v>
+      </c>
+      <c r="I764">
+        <v>22</v>
+      </c>
+      <c r="J764">
+        <v>4</v>
+      </c>
+      <c r="K764">
+        <v>4</v>
+      </c>
+      <c r="O764">
+        <v>3</v>
+      </c>
+      <c r="Q764">
+        <v>11</v>
+      </c>
+      <c r="R764">
+        <v>6</v>
+      </c>
+      <c r="S764">
+        <v>5</v>
+      </c>
+      <c r="W764">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data_polls.xlsx
+++ b/data_polls.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W764"/>
+  <dimension ref="A1:W765"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -34733,6 +34733,58 @@
         <v>10</v>
       </c>
     </row>
+    <row r="765">
+      <c r="A765" s="2">
+        <v>46110</v>
+      </c>
+      <c r="B765" s="2">
+        <v>46101</v>
+      </c>
+      <c r="C765" s="2">
+        <v>46106</v>
+      </c>
+      <c r="D765" s="2">
+        <v>46103</v>
+      </c>
+      <c r="E765" t="inlineStr">
+        <is>
+          <t>Red C</t>
+        </is>
+      </c>
+      <c r="F765">
+        <v>1010</v>
+      </c>
+      <c r="G765">
+        <v>16</v>
+      </c>
+      <c r="H765">
+        <v>18</v>
+      </c>
+      <c r="I765">
+        <v>24</v>
+      </c>
+      <c r="J765">
+        <v>4</v>
+      </c>
+      <c r="K765">
+        <v>3</v>
+      </c>
+      <c r="O765">
+        <v>3</v>
+      </c>
+      <c r="Q765">
+        <v>8</v>
+      </c>
+      <c r="R765">
+        <v>6</v>
+      </c>
+      <c r="S765">
+        <v>5</v>
+      </c>
+      <c r="W765">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data_polls.xlsx
+++ b/data_polls.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W765"/>
+  <dimension ref="A1:W766"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -34785,6 +34785,58 @@
         <v>13</v>
       </c>
     </row>
+    <row r="766">
+      <c r="A766" s="2">
+        <v>46117</v>
+      </c>
+      <c r="B766" s="2">
+        <v>46114</v>
+      </c>
+      <c r="C766" s="2">
+        <v>46115</v>
+      </c>
+      <c r="D766" s="2">
+        <v>46114</v>
+      </c>
+      <c r="E766" t="inlineStr">
+        <is>
+          <t>Ireland Thinks</t>
+        </is>
+      </c>
+      <c r="F766">
+        <v>1286</v>
+      </c>
+      <c r="G766">
+        <v>19</v>
+      </c>
+      <c r="H766">
+        <v>17</v>
+      </c>
+      <c r="I766">
+        <v>22</v>
+      </c>
+      <c r="J766">
+        <v>5</v>
+      </c>
+      <c r="K766">
+        <v>3</v>
+      </c>
+      <c r="O766">
+        <v>3</v>
+      </c>
+      <c r="Q766">
+        <v>9</v>
+      </c>
+      <c r="R766">
+        <v>6</v>
+      </c>
+      <c r="S766">
+        <v>6</v>
+      </c>
+      <c r="W766">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data_polls.xlsx
+++ b/data_polls.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W766"/>
+  <dimension ref="A1:W767"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -34837,6 +34837,58 @@
         <v>10</v>
       </c>
     </row>
+    <row r="767">
+      <c r="A767" s="2">
+        <v>46138</v>
+      </c>
+      <c r="B767" s="2">
+        <v>46129</v>
+      </c>
+      <c r="C767" s="2">
+        <v>46134</v>
+      </c>
+      <c r="D767" s="2">
+        <v>46131</v>
+      </c>
+      <c r="E767" t="inlineStr">
+        <is>
+          <t>Red C</t>
+        </is>
+      </c>
+      <c r="F767">
+        <v>1008</v>
+      </c>
+      <c r="G767">
+        <v>16</v>
+      </c>
+      <c r="H767">
+        <v>16</v>
+      </c>
+      <c r="I767">
+        <v>25</v>
+      </c>
+      <c r="J767">
+        <v>4</v>
+      </c>
+      <c r="K767">
+        <v>3</v>
+      </c>
+      <c r="O767">
+        <v>3</v>
+      </c>
+      <c r="Q767">
+        <v>8</v>
+      </c>
+      <c r="R767">
+        <v>6</v>
+      </c>
+      <c r="S767">
+        <v>7</v>
+      </c>
+      <c r="W767">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data_polls.xlsx
+++ b/data_polls.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W767"/>
+  <dimension ref="A1:W768"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -34889,6 +34889,58 @@
         <v>12</v>
       </c>
     </row>
+    <row r="768">
+      <c r="A768" s="2">
+        <v>46145</v>
+      </c>
+      <c r="B768" s="2">
+        <v>46143</v>
+      </c>
+      <c r="C768" s="2">
+        <v>46143</v>
+      </c>
+      <c r="D768" s="2">
+        <v>46143</v>
+      </c>
+      <c r="E768" t="inlineStr">
+        <is>
+          <t>Ireland Thinks</t>
+        </is>
+      </c>
+      <c r="F768">
+        <v>1774</v>
+      </c>
+      <c r="G768">
+        <v>17</v>
+      </c>
+      <c r="H768">
+        <v>17</v>
+      </c>
+      <c r="I768">
+        <v>22</v>
+      </c>
+      <c r="J768">
+        <v>4</v>
+      </c>
+      <c r="K768">
+        <v>3</v>
+      </c>
+      <c r="O768">
+        <v>2</v>
+      </c>
+      <c r="Q768">
+        <v>9</v>
+      </c>
+      <c r="R768">
+        <v>7</v>
+      </c>
+      <c r="S768">
+        <v>9</v>
+      </c>
+      <c r="W768">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data_polls.xlsx
+++ b/data_polls.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W768"/>
+  <dimension ref="A1:W769"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -34941,6 +34941,58 @@
         <v>10</v>
       </c>
     </row>
+    <row r="769">
+      <c r="A769" s="2">
+        <v>46173</v>
+      </c>
+      <c r="B769" s="2">
+        <v>46164</v>
+      </c>
+      <c r="C769" s="2">
+        <v>46169</v>
+      </c>
+      <c r="D769" s="2">
+        <v>46166</v>
+      </c>
+      <c r="E769" t="inlineStr">
+        <is>
+          <t>Red C</t>
+        </is>
+      </c>
+      <c r="F769">
+        <v>1010</v>
+      </c>
+      <c r="G769">
+        <v>15</v>
+      </c>
+      <c r="H769">
+        <v>17</v>
+      </c>
+      <c r="I769">
+        <v>21</v>
+      </c>
+      <c r="J769">
+        <v>4</v>
+      </c>
+      <c r="K769">
+        <v>3</v>
+      </c>
+      <c r="O769">
+        <v>4</v>
+      </c>
+      <c r="Q769">
+        <v>10</v>
+      </c>
+      <c r="R769">
+        <v>7</v>
+      </c>
+      <c r="S769">
+        <v>7</v>
+      </c>
+      <c r="W769">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data_polls.xlsx
+++ b/data_polls.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W769"/>
+  <dimension ref="A1:W770"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -34993,6 +34993,58 @@
         <v>12</v>
       </c>
     </row>
+    <row r="770">
+      <c r="A770" s="2">
+        <v>46180</v>
+      </c>
+      <c r="B770" s="2">
+        <v>46178</v>
+      </c>
+      <c r="C770" s="2">
+        <v>46178</v>
+      </c>
+      <c r="D770" s="2">
+        <v>46178</v>
+      </c>
+      <c r="E770" t="inlineStr">
+        <is>
+          <t>Ireland Thinks</t>
+        </is>
+      </c>
+      <c r="F770">
+        <v>1625</v>
+      </c>
+      <c r="G770">
+        <v>16</v>
+      </c>
+      <c r="H770">
+        <v>19</v>
+      </c>
+      <c r="I770">
+        <v>20</v>
+      </c>
+      <c r="J770">
+        <v>3</v>
+      </c>
+      <c r="K770">
+        <v>3</v>
+      </c>
+      <c r="O770">
+        <v>2</v>
+      </c>
+      <c r="Q770">
+        <v>12</v>
+      </c>
+      <c r="R770">
+        <v>6</v>
+      </c>
+      <c r="S770">
+        <v>9</v>
+      </c>
+      <c r="W770">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data_polls.xlsx
+++ b/data_polls.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W770"/>
+  <dimension ref="A1:W771"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -35045,6 +35045,58 @@
         <v>10</v>
       </c>
     </row>
+    <row r="771">
+      <c r="A771" s="2">
+        <v>46201</v>
+      </c>
+      <c r="B771" s="2">
+        <v>46192</v>
+      </c>
+      <c r="C771" s="2">
+        <v>46197</v>
+      </c>
+      <c r="D771" s="2">
+        <v>46194</v>
+      </c>
+      <c r="E771" t="inlineStr">
+        <is>
+          <t>Red C</t>
+        </is>
+      </c>
+      <c r="F771">
+        <v>1010</v>
+      </c>
+      <c r="G771">
+        <v>14</v>
+      </c>
+      <c r="H771">
+        <v>18</v>
+      </c>
+      <c r="I771">
+        <v>21</v>
+      </c>
+      <c r="J771">
+        <v>4</v>
+      </c>
+      <c r="K771">
+        <v>3</v>
+      </c>
+      <c r="O771">
+        <v>4</v>
+      </c>
+      <c r="Q771">
+        <v>12</v>
+      </c>
+      <c r="R771">
+        <v>6</v>
+      </c>
+      <c r="S771">
+        <v>5</v>
+      </c>
+      <c r="W771">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data_polls.xlsx
+++ b/data_polls.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W771"/>
+  <dimension ref="A1:W772"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -34998,13 +34998,13 @@
         <v>46180</v>
       </c>
       <c r="B770" s="2">
-        <v>46178</v>
+        <v>46177</v>
       </c>
       <c r="C770" s="2">
         <v>46178</v>
       </c>
       <c r="D770" s="2">
-        <v>46178</v>
+        <v>46177</v>
       </c>
       <c r="E770" t="inlineStr">
         <is>
@@ -35095,6 +35095,58 @@
       </c>
       <c r="W771">
         <v>13</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" s="2">
+        <v>46208</v>
+      </c>
+      <c r="B772" s="2">
+        <v>46206</v>
+      </c>
+      <c r="C772" s="2">
+        <v>46206</v>
+      </c>
+      <c r="D772" s="2">
+        <v>46206</v>
+      </c>
+      <c r="E772" t="inlineStr">
+        <is>
+          <t>Ireland Thinks</t>
+        </is>
+      </c>
+      <c r="F772">
+        <v>1279</v>
+      </c>
+      <c r="G772">
+        <v>17</v>
+      </c>
+      <c r="H772">
+        <v>20</v>
+      </c>
+      <c r="I772">
+        <v>19</v>
+      </c>
+      <c r="J772">
+        <v>3</v>
+      </c>
+      <c r="K772">
+        <v>3</v>
+      </c>
+      <c r="O772">
+        <v>2</v>
+      </c>
+      <c r="Q772">
+        <v>12</v>
+      </c>
+      <c r="R772">
+        <v>6</v>
+      </c>
+      <c r="S772">
+        <v>7</v>
+      </c>
+      <c r="W772">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/data_polls.xlsx
+++ b/data_polls.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W772"/>
+  <dimension ref="A1:W773"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -35149,6 +35149,58 @@
         <v>11</v>
       </c>
     </row>
+    <row r="773">
+      <c r="A773" s="2">
+        <v>46236</v>
+      </c>
+      <c r="B773" s="2">
+        <v>46234</v>
+      </c>
+      <c r="C773" s="2">
+        <v>46234</v>
+      </c>
+      <c r="D773" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E773" t="inlineStr">
+        <is>
+          <t>Ireland Thinks</t>
+        </is>
+      </c>
+      <c r="F773">
+        <v>1384</v>
+      </c>
+      <c r="G773">
+        <v>16</v>
+      </c>
+      <c r="H773">
+        <v>20</v>
+      </c>
+      <c r="I773">
+        <v>20</v>
+      </c>
+      <c r="J773">
+        <v>3</v>
+      </c>
+      <c r="K773">
+        <v>3</v>
+      </c>
+      <c r="O773">
+        <v>2</v>
+      </c>
+      <c r="Q773">
+        <v>10</v>
+      </c>
+      <c r="R773">
+        <v>7</v>
+      </c>
+      <c r="S773">
+        <v>7</v>
+      </c>
+      <c r="W773">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data_polls.xlsx
+++ b/data_polls.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W773"/>
+  <dimension ref="A1:W774"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -35201,6 +35201,58 @@
         <v>12</v>
       </c>
     </row>
+    <row r="774">
+      <c r="A774" s="2">
+        <v>46271</v>
+      </c>
+      <c r="B774" s="2">
+        <v>46177</v>
+      </c>
+      <c r="C774" s="2">
+        <v>46177</v>
+      </c>
+      <c r="D774" s="2">
+        <v>46177</v>
+      </c>
+      <c r="E774" t="inlineStr">
+        <is>
+          <t>Ireland Thinks</t>
+        </is>
+      </c>
+      <c r="F774">
+        <v>1044</v>
+      </c>
+      <c r="G774">
+        <v>17</v>
+      </c>
+      <c r="H774">
+        <v>19</v>
+      </c>
+      <c r="I774">
+        <v>21</v>
+      </c>
+      <c r="J774">
+        <v>3</v>
+      </c>
+      <c r="K774">
+        <v>3</v>
+      </c>
+      <c r="O774">
+        <v>2</v>
+      </c>
+      <c r="Q774">
+        <v>10</v>
+      </c>
+      <c r="R774">
+        <v>8</v>
+      </c>
+      <c r="S774">
+        <v>7</v>
+      </c>
+      <c r="W774">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data_polls.xlsx
+++ b/data_polls.xlsx
@@ -35206,13 +35206,13 @@
         <v>46271</v>
       </c>
       <c r="B774" s="2">
-        <v>46177</v>
+        <v>46269</v>
       </c>
       <c r="C774" s="2">
-        <v>46177</v>
+        <v>46269</v>
       </c>
       <c r="D774" s="2">
-        <v>46177</v>
+        <v>46269</v>
       </c>
       <c r="E774" t="inlineStr">
         <is>
